--- a/maintenance/Furnace63_Maintenance_Tracker_Template.xlsx
+++ b/maintenance/Furnace63_Maintenance_Tracker_Template.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,6 +539,26 @@
           <t>Tracking_Mode_norm</t>
         </is>
       </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Required Parts</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Planning months</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Estimated duration min</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -623,6 +643,22 @@
           <t>event</t>
         </is>
       </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Graphite set / insulation parts; IPA wipes / cleaning cloth</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Per-Draw/Startup</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -707,6 +743,22 @@
           <t>event</t>
         </is>
       </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Top sleeve; IPA wipes / cleaning cloth</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Per-Draw/Startup</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -791,6 +843,22 @@
           <t>event</t>
         </is>
       </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Entry sleeve; IPA wipes / cleaning cloth</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Per-Draw/Startup</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -875,6 +943,22 @@
           <t>event</t>
         </is>
       </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>IPA wipes / cleaning cloth</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Per-Draw/Startup</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -965,6 +1049,18 @@
           <t>calendar</t>
         </is>
       </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1055,6 +1151,22 @@
           <t>calendar</t>
         </is>
       </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Furnace bottom door set</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1149,6 +1261,22 @@
           <t>either</t>
         </is>
       </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Pyrometer window / cleaning kit; IPA wipes / cleaning cloth</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3-Month</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1243,6 +1371,22 @@
           <t>either</t>
         </is>
       </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Graphite set / insulation parts</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>3-Month</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1337,6 +1481,18 @@
           <t>either</t>
         </is>
       </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>6-Month</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1431,6 +1587,18 @@
           <t>either</t>
         </is>
       </c>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>6-Month</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1524,6 +1692,22 @@
         <is>
           <t>either</t>
         </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>IPA wipes / cleaning cloth</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>6-Month</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="13">
@@ -1609,6 +1793,22 @@
           <t>event</t>
         </is>
       </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Purge gas / line flush consumables</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1693,6 +1893,22 @@
           <t>event</t>
         </is>
       </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Purge gas / line flush consumables</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Per-Draw/Startup</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1781,6 +1997,22 @@
           <t>hours</t>
         </is>
       </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Furnace heating element</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>3-Month</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1868,6 +2100,22 @@
         <is>
           <t>hours</t>
         </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Bottom sleeve top cap</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>On-Condition</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/maintenance/Furnace63_Maintenance_Tracker_Template.xlsx
+++ b/maintenance/Furnace63_Maintenance_Tracker_Template.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z16"/>
+  <dimension ref="A1:AT16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,22 +541,122 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Required Parts</t>
+          <t>Required_Parts</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>Task_Group</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>Planning months</t>
+          <t>Planning_Window_Months</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Estimated duration min</t>
+          <t>Est_Duration_Min</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Task_Groups</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Test_Preset</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Test_Fields</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Test_Thresholds</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Test_Condition</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Test_Action</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Trigger_Modes</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Trigger_Hours_Source</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Trigger_Hours_Interval</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Trigger_Draws_Interval</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Trigger_Calendar_Value</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Trigger_Calendar_Unit</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Last_Done_Hours_UV1</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Last_Done_Hours_UV2</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>Mandatory_Parts</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>Conditional_Parts</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>Preparation_Lead_Days</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>Parts_Check_Lead_Days</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>Auto_Order_Mandatory_Parts</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>Last_Done_Hours_Furnace</t>
         </is>
       </c>
     </row>
@@ -599,9 +699,6 @@
           <t>event</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>63mm Furnace Manual (Soreq)</t>
@@ -625,19 +722,20 @@
           <t>Ensure furnace is cold and power isolated for any graphite handling/maintenance.</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1009</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
+        <v>1009</v>
+      </c>
+      <c r="U2" t="n">
+        <v>93</v>
+      </c>
       <c r="V2" t="inlineStr">
         <is>
           <t>event</t>
@@ -658,6 +756,15 @@
       </c>
       <c r="Z2" t="n">
         <v>45</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>249</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>249</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1009</v>
       </c>
     </row>
     <row r="3">
@@ -699,9 +806,6 @@
           <t>event</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>63mm Furnace Manual (Soreq)</t>
@@ -725,19 +829,20 @@
           <t>Soot/particle build-up can degrade fibre strength; keep components clean.</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1009</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="inlineStr"/>
+        <v>1009</v>
+      </c>
+      <c r="U3" t="n">
+        <v>93</v>
+      </c>
       <c r="V3" t="inlineStr">
         <is>
           <t>event</t>
@@ -758,6 +863,15 @@
       </c>
       <c r="Z3" t="n">
         <v>20</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>249</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>249</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1009</v>
       </c>
     </row>
     <row r="4">
@@ -799,9 +913,6 @@
           <t>event</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>63mm Furnace Manual (Soreq)</t>
@@ -825,19 +936,20 @@
           <t>Dirty/incorrect entry sleeve can contribute to contamination and contact issues.</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1009</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
+        <v>1009</v>
+      </c>
+      <c r="U4" t="n">
+        <v>93</v>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>event</t>
@@ -858,6 +970,15 @@
       </c>
       <c r="Z4" t="n">
         <v>20</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>249</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>249</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1009</v>
       </c>
     </row>
     <row r="5">
@@ -899,9 +1020,6 @@
           <t>event</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>63mm Furnace Manual (Soreq)</t>
@@ -925,19 +1043,20 @@
           <t>Entry disc can be hot after a run; use heatproof gloves and allow cool-down.</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1009</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="inlineStr"/>
+        <v>1009</v>
+      </c>
+      <c r="U5" t="n">
+        <v>93</v>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>event</t>
@@ -958,6 +1077,15 @@
       </c>
       <c r="Z5" t="n">
         <v>20</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>249</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>249</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1009</v>
       </c>
     </row>
     <row r="6">
@@ -999,7 +1127,6 @@
           <t>calendar</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>months</t>
@@ -1031,25 +1158,19 @@
           <t>Investigate any alarm/interlock trigger immediately before operation.</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
-        </is>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
+          <t>2026-04-02</t>
+        </is>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
-      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
           <t>calendar</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
           <t>Weekly</t>
@@ -1101,7 +1222,6 @@
           <t>calendar</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>months</t>
@@ -1133,19 +1253,14 @@
           <t>Door condition affects gas curtain and can impact fibre contact/strength.</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
-        </is>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
+          <t>2026-03-24</t>
+        </is>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
-      <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
           <t>calendar</t>
@@ -1190,11 +1305,11 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>1500</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>months OR 1500 hours</t>
+          <t>hours</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1204,12 +1319,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>either</t>
+          <t>hours</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>OperatingHours</t>
+          <t>Furnace</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1243,19 +1358,20 @@
           <t>Pyrometer misalignment/dirty window can cause temperature control errors.</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="inlineStr"/>
+        <v>35</v>
+      </c>
+      <c r="U8" t="n">
+        <v>94</v>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>either</t>
@@ -1268,7 +1384,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>3-Month</t>
+          <t>3-Month, Hours</t>
         </is>
       </c>
       <c r="Y8" t="n">
@@ -1276,6 +1392,44 @@
       </c>
       <c r="Z8" t="n">
         <v>60</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>3-Month, Hours</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>hours</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>furnace</t>
+        </is>
+      </c>
+      <c r="AI8" t="n">
+        <v>1500</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>days</t>
+        </is>
+      </c>
+      <c r="AM8" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>250</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="9">
@@ -1353,19 +1507,17 @@
           <t>Do NOT use abrasive pads on the 'painted' radiation shield surfaces.</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="inlineStr"/>
+        <v>35</v>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>either</t>
@@ -1386,6 +1538,25 @@
       </c>
       <c r="Z9" t="n">
         <v>45</v>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>Graphite set / insulation parts</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AT9" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="10">
@@ -1463,10 +1634,9 @@
           <t>Electrical hazard: isolate electrical power before inspection.</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="S10" t="n">
@@ -1475,13 +1645,11 @@
       <c r="T10" t="n">
         <v>0</v>
       </c>
-      <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
           <t>either</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
           <t>6-Month</t>
@@ -1492,6 +1660,9 @@
       </c>
       <c r="Z10" t="n">
         <v>15</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1569,10 +1740,9 @@
           <t>Working at height: follow safety rules and use harness/guard rails as required.</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="S11" t="n">
@@ -1581,13 +1751,11 @@
       <c r="T11" t="n">
         <v>0</v>
       </c>
-      <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
           <t>either</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
           <t>6-Month</t>
@@ -1598,6 +1766,9 @@
       </c>
       <c r="Z11" t="n">
         <v>60</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1675,10 +1846,9 @@
           <t>Ensure vacuum pump is OFF during storage checks to avoid masking leaks.</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="S12" t="n">
@@ -1687,7 +1857,6 @@
       <c r="T12" t="n">
         <v>0</v>
       </c>
-      <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
           <t>either</t>
@@ -1708,6 +1877,9 @@
       </c>
       <c r="Z12" t="n">
         <v>30</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1749,9 +1921,6 @@
           <t>event</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>63mm Furnace Manual (Soreq)</t>
@@ -1775,19 +1944,20 @@
           <t>If vacuum cannot reach ~-0.85 bar, check seals and repeat. Monitor first auto-cycle if using MFC auto purge.</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1009</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="inlineStr"/>
+        <v>1009</v>
+      </c>
+      <c r="U13" t="n">
+        <v>93</v>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>event</t>
@@ -1808,6 +1978,15 @@
       </c>
       <c r="Z13" t="n">
         <v>25</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>249</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>249</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1009</v>
       </c>
     </row>
     <row r="14">
@@ -1849,9 +2028,6 @@
           <t>event</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>63mm Furnace Manual (Soreq)</t>
@@ -1875,19 +2051,20 @@
           <t>Progressive rise indicates a leak in seals or gas delivery; rectify before running.</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1009</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="inlineStr"/>
+        <v>1009</v>
+      </c>
+      <c r="U14" t="n">
+        <v>93</v>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>event</t>
@@ -1908,6 +2085,15 @@
       </c>
       <c r="Z14" t="n">
         <v>25</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>249</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>249</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1009</v>
       </c>
     </row>
     <row r="15">
@@ -1954,8 +2140,6 @@
           <t>OperatingHours</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>63mm Furnace Manual (Soreq)</t>
@@ -1979,19 +2163,12 @@
           <t>Element life is strongly affected by oxygen ingress and operating procedure.</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>2025-01-22</t>
-        </is>
-      </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>685</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="inlineStr"/>
+        <v>685</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>hours</t>
@@ -2012,6 +2189,9 @@
       </c>
       <c r="Z15" t="n">
         <v>45</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>685</v>
       </c>
     </row>
     <row r="16">
@@ -2058,8 +2238,6 @@
           <t>OperatingHours</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>63mm Furnace Manual (Soreq)</t>
@@ -2083,19 +2261,12 @@
           <t>Top cap life depends strongly on avoiding air entry; poor procedures drastically reduce life.</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>2025-01-22</t>
-        </is>
-      </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>847.5</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="inlineStr"/>
+        <v>847.5</v>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>hours</t>
@@ -2116,6 +2287,9 @@
       </c>
       <c r="Z16" t="n">
         <v>45</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>847.5</v>
       </c>
     </row>
   </sheetData>
